--- a/Data/06_VehicleSensorNumbers.xlsx
+++ b/Data/06_VehicleSensorNumbers.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,15 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -110,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -136,6 +145,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -4423,22 +4434,22 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -4458,22 +4469,22 @@
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
@@ -4493,7 +4504,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>1</v>
@@ -4502,13 +4513,13 @@
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -4528,22 +4539,22 @@
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
@@ -4563,7 +4574,7 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>1</v>
@@ -4598,7 +4609,7 @@
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" s="5" t="n">
         <v>1</v>
@@ -4633,13 +4644,13 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>4</v>
@@ -4668,13 +4679,13 @@
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G119" s="5" t="n">
         <v>4</v>
@@ -4703,19 +4714,19 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" s="3" t="n">
         <v>1</v>
@@ -4738,19 +4749,19 @@
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" s="5" t="n">
         <v>1</v>
@@ -4773,19 +4784,19 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" s="3" t="n">
         <v>1</v>
@@ -4808,19 +4819,19 @@
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" s="5" t="n">
         <v>2</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" s="5" t="n">
         <v>2</v>
@@ -4843,7 +4854,7 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>8</v>
@@ -4878,13 +4889,13 @@
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" s="5" t="n">
         <v>1</v>
@@ -4893,7 +4904,7 @@
         <v>1</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -4913,22 +4924,22 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H126" s="3" t="n">
         <v>1</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
@@ -4948,19 +4959,19 @@
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" s="5" t="n">
         <v>1</v>
@@ -4983,7 +4994,7 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>1</v>
@@ -5021,19 +5032,19 @@
         <v>0</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5056,19 +5067,19 @@
         <v>0</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -8899,7 +8910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9045,6 +9056,334 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-07 -- ADAS COUNT BASIS CHANGED TO 'GIVEN PRESENT' (reading 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>A 0 in an ADAS Min column used to mean 'this segment does not have the component'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>That job now belongs to presence(component,segment,year) from 19_ Presence_per_Tier,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>so keeping the zero discounted the same absence twice. Worse, 0-0 rows made growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>impossible: AB side cameras, corner radars, driver monitoring and lidar were pinned at</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>zero for every tier and year (presence 0.87-0.92 at 2070 x count 0 = 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Ranges now mean: HOW MANY a vehicle carries GIVEN it has the component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Effect on expected ADAS sensors/vehicle: AB 8.6-&gt;18.1 at 2025 and growth 1.36x-&gt;1.75x;</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>CD 27.2-&gt;30.2, 1.24x-&gt;1.32x; EF 40.2-&gt;41.6, 1.07x-&gt;1.10x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>STILL OPEN 1: ultrasonics appear under BOTH 'Ultrasonic sensors' and 'Parking assist</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>ECU' at the same 8-12. Reading 1 no longer masks that with a 0 minimum. Needs a decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>STILL OPEN 2: sheet 'Sensor Type Summary' is DERIVED from this sheet and is now STALE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>It is not read by SensorNumbersMC.py (which uses sheet 0 only), so nothing is broken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Regenerating it needs care: it holds BOTH 'Hall sensor' and 'hall sensor' as separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>rows, so a case-insensitive rebuild writes the merged total into both and double-counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-07 -- OPTION A: CAMERA COUNTS RAISED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Reason (user): cameras are safety-critical, so viewing areas carry REDUNDANCY and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>suite must avoid DEAD SPOTS. The file had exactly one camera per viewing direction --</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>1 forward, 1 rearward, 2 side -- i.e. no redundancy anywhere, and no front-corner cover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Ceiling was AB 5 / CD 5 / EF 6 cameras against 19_ sheet Tiers expecting 8-12 at H3,</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>so the sensor model could not reach the wiring model's camera count at any high tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Raised: front 1-2/1-3/2-3 (mono-&gt;stereo-&gt;trifocal), rear 1-1/1-2/1-2 (reversing + rear</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>ADAS), side 2-2/2-4/4-4 (surround + blind spot), DMS 1-1/1-1/1-2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Companion element rows (temperature sensor, IR LED array) were moved with their primary,</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>or 19_ sheet Modules_vs_Elements would no longer hold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>New ceiling AB 7 / CD 12 / EF 13 -- overlaps Tiers 8-12 at the tiers that matter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>OPTION B -- NOT DONE, kept as a documented alternative. See docs/SENSOR_MODEL_DESIGN.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>section 10 item 5. It adds two components that do not exist anywhere in the project:</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>front-corner / A-pillar cameras (cross-traffic at junctions -- the real dead spot, today</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>folded into 'Side / mirror cameras'), and a cabin / child-presence camera (occupant</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>detection here is pressure mats, capacitive and belt buckles -- NOT vision, while Euro</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>NCAP and GSR-2 phase 2 push camera or radar child presence detection).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-07 -- PARKING ASSIST ECU SENSOR ROWS SET TO ZERO (double-count removed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>The ECU carried 'ultrasonic sensor' and 'camera input' with ranges IDENTICAL to</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>'Ultrasonic sensors' and to the surround cameras. It is the CONTROLLER for those</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>sensors, not a second set of them, so the model was counting each sensor twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Measured effect before the fix: EF reported 19.7 ultrasonic sensors per car</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>(9.8 'ultrasonic sensor' + 9.9 'ultrasonic transducer'), CD 15.4, AB 7.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>A full ring is 6 front + 6 rear = 12, so ~20 was roughly double reality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>User judgement (2026-08-07): 8-12 is right for EF; more would be 'a lot of sensors</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>around a car'. The 13-16 figure previously quoted in project documents could not be</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>traced to a primary source and should not be used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Rows are ZEROED rather than deleted, so the component stays visible and the decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>stays reversible. The ECU itself remains a component; it simply owns no sensors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>NOTE: Tiers in 19_ is derived from PRIMARY elements only, and Parking assist ECU has</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>no primary element, so 19_ and V15 are unaffected by this change.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
